--- a/strategy_recommended_runner/outputs/rebound_top3_ranking_today.xlsx
+++ b/strategy_recommended_runner/outputs/rebound_top3_ranking_today.xlsx
@@ -21,13 +21,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +49,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,52 +433,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>备选</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rank_score</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>probability_score</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>current_drawdown_pct</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>latest_turn</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>current_low_to_latest_pct</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>history_success_rate_pct</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>latest_close</t>
         </is>
@@ -601,92 +613,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rank_score</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>probability_score</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>current_drawdown_pct</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>current_low_to_latest_pct</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>latest_turn</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>latest_pct_chg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>current_stage</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>current_is_bottom_confirmed</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>latest_close</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>current_low_price</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>current_top_price</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>history_success_rate_pct</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>history_sample_count</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>history_success_count</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
@@ -1219,92 +1231,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rank_score</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>probability_score</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>current_drawdown_pct</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>current_low_to_latest_pct</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>latest_turn</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>latest_pct_chg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>current_stage</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>current_is_bottom_confirmed</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>latest_close</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>current_low_price</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>current_top_price</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>history_success_rate_pct</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>history_sample_count</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>history_success_count</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
@@ -11693,10 +11705,10 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>61.70350350050646</v>
+        <v>61.70350350050647</v>
       </c>
       <c r="E164" t="n">
-        <v>56.03172111795435</v>
+        <v>56.03172111795436</v>
       </c>
       <c r="F164" t="n">
         <v>29.41176470588236</v>
@@ -15277,137 +15289,137 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>rank_score</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>probability_score</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>current_stage</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>latest_date</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>latest_close</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>current_top_price</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>current_low_date</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>current_low_price</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>current_low_to_latest_pct</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>current_low_to_high_pct</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>current_drawdown_pct</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>close_drawdown_pct</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>current_is_bottom_confirmed</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>latest_pct_chg</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>latest_turn</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>historical_valid_event_count</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>history_sample_count</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>history_success_count</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>history_success_rate_pct</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>history_avg_rebound_pct</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>history_max_rebound_pct</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>upside_to_20pct_target_pct</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>risk_back_to_low_pct</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
@@ -15871,7 +15883,7 @@
         <v>66.66666666666666</v>
       </c>
       <c r="W6" t="n">
-        <v>25.05943657759895</v>
+        <v>25.05943657759896</v>
       </c>
       <c r="X6" t="n">
         <v>33.26359832635983</v>
@@ -16821,7 +16833,7 @@
         <v>60</v>
       </c>
       <c r="W16" t="n">
-        <v>31.23556141444489</v>
+        <v>31.23556141444491</v>
       </c>
       <c r="X16" t="n">
         <v>37.95180722891568</v>
@@ -17106,7 +17118,7 @@
         <v>56.25</v>
       </c>
       <c r="W19" t="n">
-        <v>38.24386332079093</v>
+        <v>38.24386332079092</v>
       </c>
       <c r="X19" t="n">
         <v>81.5282392026578</v>
@@ -18246,7 +18258,7 @@
         <v>50</v>
       </c>
       <c r="W31" t="n">
-        <v>33.91793779795372</v>
+        <v>33.91793779795371</v>
       </c>
       <c r="X31" t="n">
         <v>37.63608087091757</v>
@@ -19481,7 +19493,7 @@
         <v>43.47826086956522</v>
       </c>
       <c r="W44" t="n">
-        <v>31.029760840556</v>
+        <v>31.02976084055601</v>
       </c>
       <c r="X44" t="n">
         <v>53.51562499999998</v>
@@ -20336,7 +20348,7 @@
         <v>54.54545454545454</v>
       </c>
       <c r="W53" t="n">
-        <v>29.9465154336244</v>
+        <v>29.94651543362441</v>
       </c>
       <c r="X53" t="n">
         <v>55.84045584045584</v>
@@ -21571,7 +21583,7 @@
         <v>36.36363636363637</v>
       </c>
       <c r="W66" t="n">
-        <v>69.40710351619819</v>
+        <v>69.40710351619818</v>
       </c>
       <c r="X66" t="n">
         <v>114.6478873239437</v>
@@ -24611,7 +24623,7 @@
         <v>50</v>
       </c>
       <c r="W98" t="n">
-        <v>35.01991743580866</v>
+        <v>35.01991743580865</v>
       </c>
       <c r="X98" t="n">
         <v>57.03937007874016</v>
@@ -24991,7 +25003,7 @@
         <v>36.36363636363637</v>
       </c>
       <c r="W102" t="n">
-        <v>66.24257752712205</v>
+        <v>66.24257752712204</v>
       </c>
       <c r="X102" t="n">
         <v>150.8250825082508</v>
@@ -27746,7 +27758,7 @@
         <v>42.30769230769231</v>
       </c>
       <c r="W131" t="n">
-        <v>36.23959559883681</v>
+        <v>36.2395955988368</v>
       </c>
       <c r="X131" t="n">
         <v>90.05145797598628</v>
@@ -28791,7 +28803,7 @@
         <v>25</v>
       </c>
       <c r="W142" t="n">
-        <v>35.31603140766591</v>
+        <v>35.31603140766592</v>
       </c>
       <c r="X142" t="n">
         <v>50.00000000000001</v>
@@ -28981,7 +28993,7 @@
         <v>30</v>
       </c>
       <c r="W144" t="n">
-        <v>31.48974966494908</v>
+        <v>31.48974966494909</v>
       </c>
       <c r="X144" t="n">
         <v>32.93413173652696</v>
@@ -29266,7 +29278,7 @@
         <v>26.66666666666667</v>
       </c>
       <c r="W147" t="n">
-        <v>34.16516874416609</v>
+        <v>34.1651687441661</v>
       </c>
       <c r="X147" t="n">
         <v>44.40363228242016</v>
@@ -30808,10 +30820,10 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>61.70350350050646</v>
+        <v>61.70350350050647</v>
       </c>
       <c r="C164" t="n">
-        <v>56.03172111795435</v>
+        <v>56.03172111795436</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -32116,7 +32128,7 @@
         <v>25</v>
       </c>
       <c r="W177" t="n">
-        <v>28.13075502264662</v>
+        <v>28.13075502264661</v>
       </c>
       <c r="X177" t="n">
         <v>32.21153846153846</v>
@@ -36138,12 +36150,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>项目</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
